--- a/excelDataSource/20260623_涨停复盘_verified.xlsx
+++ b/excelDataSource/20260623_涨停复盘_verified.xlsx
@@ -4083,14 +4083,10 @@
           <t>10:55</t>
         </is>
       </c>
-      <c r="E95" t="inlineStr">
-        <is>
-          <t>18.13%</t>
-        </is>
-      </c>
+      <c r="E95" t="inlineStr"/>
       <c r="F95" t="inlineStr">
         <is>
-          <t>半导体</t>
+          <t>18.13% 半导体</t>
         </is>
       </c>
     </row>
@@ -4115,14 +4111,10 @@
           <t>10:23</t>
         </is>
       </c>
-      <c r="E96" t="inlineStr">
-        <is>
-          <t>15.71%</t>
-        </is>
-      </c>
+      <c r="E96" t="inlineStr"/>
       <c r="F96" t="inlineStr">
         <is>
-          <t>半导体</t>
+          <t>15.71% 半导体</t>
         </is>
       </c>
     </row>
@@ -4147,14 +4139,10 @@
           <t>10:50</t>
         </is>
       </c>
-      <c r="E97" t="inlineStr">
-        <is>
-          <t>12.42%</t>
-        </is>
-      </c>
+      <c r="E97" t="inlineStr"/>
       <c r="F97" t="inlineStr">
         <is>
-          <t>国产芯片</t>
+          <t>12.42% 国产芯片</t>
         </is>
       </c>
     </row>
@@ -4179,14 +4167,10 @@
           <t>9:33</t>
         </is>
       </c>
-      <c r="E98" t="inlineStr">
-        <is>
-          <t>11.24%</t>
-        </is>
-      </c>
+      <c r="E98" t="inlineStr"/>
       <c r="F98" t="inlineStr">
         <is>
-          <t>液冷服务器</t>
+          <t>11.24% 液冷服务器</t>
         </is>
       </c>
     </row>
@@ -4211,14 +4195,10 @@
           <t>10:39</t>
         </is>
       </c>
-      <c r="E99" t="inlineStr">
-        <is>
-          <t>11.13%</t>
-        </is>
-      </c>
+      <c r="E99" t="inlineStr"/>
       <c r="F99" t="inlineStr">
         <is>
-          <t>医药</t>
+          <t>11.13% 医药</t>
         </is>
       </c>
     </row>
@@ -4243,14 +4223,10 @@
           <t>9:48</t>
         </is>
       </c>
-      <c r="E100" t="inlineStr">
-        <is>
-          <t>10.15%</t>
-        </is>
-      </c>
+      <c r="E100" t="inlineStr"/>
       <c r="F100" t="inlineStr">
         <is>
-          <t>地产</t>
+          <t>10.15% 地产</t>
         </is>
       </c>
     </row>
@@ -4275,14 +4251,10 @@
           <t>10:31</t>
         </is>
       </c>
-      <c r="E101" t="inlineStr">
-        <is>
-          <t>9.99%</t>
-        </is>
-      </c>
+      <c r="E101" t="inlineStr"/>
       <c r="F101" t="inlineStr">
         <is>
-          <t>PCB板</t>
+          <t>9.99% PCB板</t>
         </is>
       </c>
     </row>
@@ -4307,14 +4279,10 @@
           <t>10:00</t>
         </is>
       </c>
-      <c r="E102" t="inlineStr">
-        <is>
-          <t>9.87%</t>
-        </is>
-      </c>
+      <c r="E102" t="inlineStr"/>
       <c r="F102" t="inlineStr">
         <is>
-          <t>大金融</t>
+          <t>9.87% 大金融</t>
         </is>
       </c>
     </row>
@@ -4339,14 +4307,10 @@
           <t>10:18</t>
         </is>
       </c>
-      <c r="E103" t="inlineStr">
-        <is>
-          <t>8.81%</t>
-        </is>
-      </c>
+      <c r="E103" t="inlineStr"/>
       <c r="F103" t="inlineStr">
         <is>
-          <t>光通信</t>
+          <t>8.81% 光通信</t>
         </is>
       </c>
     </row>
@@ -4371,14 +4335,10 @@
           <t>13:24</t>
         </is>
       </c>
-      <c r="E104" t="inlineStr">
-        <is>
-          <t>8.51%</t>
-        </is>
-      </c>
+      <c r="E104" t="inlineStr"/>
       <c r="F104" t="inlineStr">
         <is>
-          <t>国产芯片</t>
+          <t>8.51% 国产芯片</t>
         </is>
       </c>
     </row>
@@ -4403,14 +4363,10 @@
           <t>9:34</t>
         </is>
       </c>
-      <c r="E105" t="inlineStr">
-        <is>
-          <t>8.25%</t>
-        </is>
-      </c>
+      <c r="E105" t="inlineStr"/>
       <c r="F105" t="inlineStr">
         <is>
-          <t>数据中心散热</t>
+          <t>8.25% 数据中心散热</t>
         </is>
       </c>
     </row>
@@ -4435,14 +4391,10 @@
           <t>10:18</t>
         </is>
       </c>
-      <c r="E106" t="inlineStr">
-        <is>
-          <t>8.08%</t>
-        </is>
-      </c>
+      <c r="E106" t="inlineStr"/>
       <c r="F106" t="inlineStr">
         <is>
-          <t>医药</t>
+          <t>8.08% 医药</t>
         </is>
       </c>
     </row>
@@ -4467,14 +4419,10 @@
           <t>13:43</t>
         </is>
       </c>
-      <c r="E107" t="inlineStr">
-        <is>
-          <t>7.92%</t>
-        </is>
-      </c>
+      <c r="E107" t="inlineStr"/>
       <c r="F107" t="inlineStr">
         <is>
-          <t>其他</t>
+          <t>7.92% 其他</t>
         </is>
       </c>
     </row>
@@ -4499,14 +4447,10 @@
           <t>14:49</t>
         </is>
       </c>
-      <c r="E108" t="inlineStr">
-        <is>
-          <t>7.73%</t>
-        </is>
-      </c>
+      <c r="E108" t="inlineStr"/>
       <c r="F108" t="inlineStr">
         <is>
-          <t>大消费</t>
+          <t>7.73% 大消费</t>
         </is>
       </c>
     </row>
@@ -4531,14 +4475,10 @@
           <t>9:49</t>
         </is>
       </c>
-      <c r="E109" t="inlineStr">
-        <is>
-          <t>7.53%</t>
-        </is>
-      </c>
+      <c r="E109" t="inlineStr"/>
       <c r="F109" t="inlineStr">
         <is>
-          <t>医疗医药</t>
+          <t>7.53% 医疗医药</t>
         </is>
       </c>
     </row>
@@ -4563,14 +4503,10 @@
           <t>10:59</t>
         </is>
       </c>
-      <c r="E110" t="inlineStr">
-        <is>
-          <t>7.47%</t>
-        </is>
-      </c>
+      <c r="E110" t="inlineStr"/>
       <c r="F110" t="inlineStr">
         <is>
-          <t>医药</t>
+          <t>7.47% 医药</t>
         </is>
       </c>
     </row>
@@ -4595,14 +4531,10 @@
           <t>13:31</t>
         </is>
       </c>
-      <c r="E111" t="inlineStr">
-        <is>
-          <t>7.26%</t>
-        </is>
-      </c>
+      <c r="E111" t="inlineStr"/>
       <c r="F111" t="inlineStr">
         <is>
-          <t>其他</t>
+          <t>7.26% 其他</t>
         </is>
       </c>
     </row>
@@ -4627,14 +4559,10 @@
           <t>10:38</t>
         </is>
       </c>
-      <c r="E112" t="inlineStr">
-        <is>
-          <t>7.21%</t>
-        </is>
-      </c>
+      <c r="E112" t="inlineStr"/>
       <c r="F112" t="inlineStr">
         <is>
-          <t>大消费</t>
+          <t>7.21% 大消费</t>
         </is>
       </c>
     </row>
@@ -4659,14 +4587,10 @@
           <t>10:20</t>
         </is>
       </c>
-      <c r="E113" t="inlineStr">
-        <is>
-          <t>7.16%</t>
-        </is>
-      </c>
+      <c r="E113" t="inlineStr"/>
       <c r="F113" t="inlineStr">
         <is>
-          <t>国产芯片</t>
+          <t>7.16% 国产芯片</t>
         </is>
       </c>
     </row>
@@ -4691,14 +4615,10 @@
           <t>9:50</t>
         </is>
       </c>
-      <c r="E114" t="inlineStr">
-        <is>
-          <t>6.62%</t>
-        </is>
-      </c>
+      <c r="E114" t="inlineStr"/>
       <c r="F114" t="inlineStr">
         <is>
-          <t>医疗医药</t>
+          <t>6.62% 医疗医药</t>
         </is>
       </c>
     </row>
@@ -4723,14 +4643,10 @@
           <t>9:33</t>
         </is>
       </c>
-      <c r="E115" t="inlineStr">
-        <is>
-          <t>6.53%</t>
-        </is>
-      </c>
+      <c r="E115" t="inlineStr"/>
       <c r="F115" t="inlineStr">
         <is>
-          <t>液冷服务器</t>
+          <t>6.53% 液冷服务器</t>
         </is>
       </c>
     </row>
@@ -4755,14 +4671,10 @@
           <t>9:49</t>
         </is>
       </c>
-      <c r="E116" t="inlineStr">
-        <is>
-          <t>6.51%</t>
-        </is>
-      </c>
+      <c r="E116" t="inlineStr"/>
       <c r="F116" t="inlineStr">
         <is>
-          <t>大金融</t>
+          <t>6.51% 大金融</t>
         </is>
       </c>
     </row>
@@ -4787,14 +4699,10 @@
           <t>9:25</t>
         </is>
       </c>
-      <c r="E117" t="inlineStr">
-        <is>
-          <t>6.35%</t>
-        </is>
-      </c>
+      <c r="E117" t="inlineStr"/>
       <c r="F117" t="inlineStr">
         <is>
-          <t>有色金属</t>
+          <t>6.35% 有色金属</t>
         </is>
       </c>
     </row>
@@ -4819,14 +4727,10 @@
           <t>13:37</t>
         </is>
       </c>
-      <c r="E118" t="inlineStr">
-        <is>
-          <t>6.24%</t>
-        </is>
-      </c>
+      <c r="E118" t="inlineStr"/>
       <c r="F118" t="inlineStr">
         <is>
-          <t>机器人</t>
+          <t>6.24% 机器人</t>
         </is>
       </c>
     </row>
@@ -4851,14 +4755,10 @@
           <t>11:07</t>
         </is>
       </c>
-      <c r="E119" t="inlineStr">
-        <is>
-          <t>6.19%</t>
-        </is>
-      </c>
+      <c r="E119" t="inlineStr"/>
       <c r="F119" t="inlineStr">
         <is>
-          <t>影视</t>
+          <t>6.19% 影视</t>
         </is>
       </c>
     </row>
@@ -4883,14 +4783,10 @@
           <t>10:21</t>
         </is>
       </c>
-      <c r="E120" t="inlineStr">
-        <is>
-          <t>6.14%</t>
-        </is>
-      </c>
+      <c r="E120" t="inlineStr"/>
       <c r="F120" t="inlineStr">
         <is>
-          <t>机器人</t>
+          <t>6.14% 机器人</t>
         </is>
       </c>
     </row>
@@ -4915,14 +4811,10 @@
           <t>9:51</t>
         </is>
       </c>
-      <c r="E121" t="inlineStr">
-        <is>
-          <t>5.73%</t>
-        </is>
-      </c>
+      <c r="E121" t="inlineStr"/>
       <c r="F121" t="inlineStr">
         <is>
-          <t>医药</t>
+          <t>5.73% 医药</t>
         </is>
       </c>
     </row>
@@ -4947,14 +4839,10 @@
           <t>9:58</t>
         </is>
       </c>
-      <c r="E122" t="inlineStr">
-        <is>
-          <t>5.60%</t>
-        </is>
-      </c>
+      <c r="E122" t="inlineStr"/>
       <c r="F122" t="inlineStr">
         <is>
-          <t>石油化工</t>
+          <t>5.60% 石油化工</t>
         </is>
       </c>
     </row>
@@ -4979,14 +4867,10 @@
           <t>9:25</t>
         </is>
       </c>
-      <c r="E123" t="inlineStr">
-        <is>
-          <t>5.41%</t>
-        </is>
-      </c>
+      <c r="E123" t="inlineStr"/>
       <c r="F123" t="inlineStr">
         <is>
-          <t>数据中心散热</t>
+          <t>5.41% 数据中心散热</t>
         </is>
       </c>
     </row>
@@ -5011,14 +4895,10 @@
           <t>9:25</t>
         </is>
       </c>
-      <c r="E124" t="inlineStr">
-        <is>
-          <t>5.40%</t>
-        </is>
-      </c>
+      <c r="E124" t="inlineStr"/>
       <c r="F124" t="inlineStr">
         <is>
-          <t>数据中心散热</t>
+          <t>5.40% 数据中心散热</t>
         </is>
       </c>
     </row>
@@ -5043,14 +4923,10 @@
           <t>9:30</t>
         </is>
       </c>
-      <c r="E125" t="inlineStr">
-        <is>
-          <t>5.20%</t>
-        </is>
-      </c>
+      <c r="E125" t="inlineStr"/>
       <c r="F125" t="inlineStr">
         <is>
-          <t>有色金属</t>
+          <t>5.20% 有色金属</t>
         </is>
       </c>
     </row>
@@ -5075,14 +4951,10 @@
           <t>9:31</t>
         </is>
       </c>
-      <c r="E126" t="inlineStr">
-        <is>
-          <t>5.19%</t>
-        </is>
-      </c>
+      <c r="E126" t="inlineStr"/>
       <c r="F126" t="inlineStr">
         <is>
-          <t>培育钻石</t>
+          <t>5.19% 培育钻石</t>
         </is>
       </c>
     </row>
@@ -5107,14 +4979,10 @@
           <t>10:00</t>
         </is>
       </c>
-      <c r="E127" t="inlineStr">
-        <is>
-          <t>5.02%</t>
-        </is>
-      </c>
+      <c r="E127" t="inlineStr"/>
       <c r="F127" t="inlineStr">
         <is>
-          <t>有色金属</t>
+          <t>5.02% 有色金属</t>
         </is>
       </c>
     </row>
@@ -5139,14 +5007,10 @@
           <t>9:25</t>
         </is>
       </c>
-      <c r="E128" t="inlineStr">
-        <is>
-          <t>4.51%</t>
-        </is>
-      </c>
+      <c r="E128" t="inlineStr"/>
       <c r="F128" t="inlineStr">
         <is>
-          <t>数据中心散热</t>
+          <t>4.51% 数据中心散热</t>
         </is>
       </c>
     </row>
@@ -5171,14 +5035,10 @@
           <t>9:37</t>
         </is>
       </c>
-      <c r="E129" t="inlineStr">
-        <is>
-          <t>4.50%</t>
-        </is>
-      </c>
+      <c r="E129" t="inlineStr"/>
       <c r="F129" t="inlineStr">
         <is>
-          <t>大金融</t>
+          <t>4.50% 大金融</t>
         </is>
       </c>
     </row>
@@ -5203,14 +5063,10 @@
           <t>9:25</t>
         </is>
       </c>
-      <c r="E130" t="inlineStr">
-        <is>
-          <t>4.42%</t>
-        </is>
-      </c>
+      <c r="E130" t="inlineStr"/>
       <c r="F130" t="inlineStr">
         <is>
-          <t>有色金属</t>
+          <t>4.42% 有色金属</t>
         </is>
       </c>
     </row>
@@ -5235,14 +5091,10 @@
           <t>9:57</t>
         </is>
       </c>
-      <c r="E131" t="inlineStr">
-        <is>
-          <t>4.19%</t>
-        </is>
-      </c>
+      <c r="E131" t="inlineStr"/>
       <c r="F131" t="inlineStr">
         <is>
-          <t>其他</t>
+          <t>4.19% 其他</t>
         </is>
       </c>
     </row>
@@ -5267,14 +5119,10 @@
           <t>9:37</t>
         </is>
       </c>
-      <c r="E132" t="inlineStr">
-        <is>
-          <t>4.19%</t>
-        </is>
-      </c>
+      <c r="E132" t="inlineStr"/>
       <c r="F132" t="inlineStr">
         <is>
-          <t>光通信</t>
+          <t>4.19% 光通信</t>
         </is>
       </c>
     </row>
@@ -5299,14 +5147,10 @@
           <t>10:32</t>
         </is>
       </c>
-      <c r="E133" t="inlineStr">
-        <is>
-          <t>3.87%</t>
-        </is>
-      </c>
+      <c r="E133" t="inlineStr"/>
       <c r="F133" t="inlineStr">
         <is>
-          <t>机器人</t>
+          <t>3.87% 机器人</t>
         </is>
       </c>
     </row>
@@ -5331,14 +5175,10 @@
           <t>9:32</t>
         </is>
       </c>
-      <c r="E134" t="inlineStr">
-        <is>
-          <t>3.58%</t>
-        </is>
-      </c>
+      <c r="E134" t="inlineStr"/>
       <c r="F134" t="inlineStr">
         <is>
-          <t>有色金属</t>
+          <t>3.58% 有色金属</t>
         </is>
       </c>
     </row>
@@ -5363,14 +5203,10 @@
           <t>10:05</t>
         </is>
       </c>
-      <c r="E135" t="inlineStr">
-        <is>
-          <t>3.52%</t>
-        </is>
-      </c>
+      <c r="E135" t="inlineStr"/>
       <c r="F135" t="inlineStr">
         <is>
-          <t>机器人</t>
+          <t>3.52% 机器人</t>
         </is>
       </c>
     </row>
@@ -5395,14 +5231,10 @@
           <t>9:25</t>
         </is>
       </c>
-      <c r="E136" t="inlineStr">
-        <is>
-          <t>2.56%</t>
-        </is>
-      </c>
+      <c r="E136" t="inlineStr"/>
       <c r="F136" t="inlineStr">
         <is>
-          <t>数据中心散热</t>
+          <t>2.56% 数据中心散热</t>
         </is>
       </c>
     </row>
@@ -5427,14 +5259,10 @@
           <t>9:25</t>
         </is>
       </c>
-      <c r="E137" t="inlineStr">
-        <is>
-          <t>2.11%</t>
-        </is>
-      </c>
+      <c r="E137" t="inlineStr"/>
       <c r="F137" t="inlineStr">
         <is>
-          <t>公告</t>
+          <t>2.11% 公告</t>
         </is>
       </c>
     </row>
@@ -5459,14 +5287,10 @@
           <t>9:30</t>
         </is>
       </c>
-      <c r="E138" t="inlineStr">
-        <is>
-          <t>1.07%</t>
-        </is>
-      </c>
+      <c r="E138" t="inlineStr"/>
       <c r="F138" t="inlineStr">
         <is>
-          <t>液冷服务器</t>
+          <t>1.07% 液冷服务器</t>
         </is>
       </c>
     </row>
@@ -5491,14 +5315,10 @@
           <t>9:32</t>
         </is>
       </c>
-      <c r="E139" t="inlineStr">
-        <is>
-          <t>0.92%</t>
-        </is>
-      </c>
+      <c r="E139" t="inlineStr"/>
       <c r="F139" t="inlineStr">
         <is>
-          <t>石油化工</t>
+          <t>0.92% 石油化工</t>
         </is>
       </c>
     </row>
@@ -5523,14 +5343,10 @@
           <t>9:30</t>
         </is>
       </c>
-      <c r="E140" t="inlineStr">
-        <is>
-          <t>0.28%</t>
-        </is>
-      </c>
+      <c r="E140" t="inlineStr"/>
       <c r="F140" t="inlineStr">
         <is>
-          <t>其他</t>
+          <t>0.28% 其他</t>
         </is>
       </c>
     </row>
@@ -5555,14 +5371,10 @@
           <t>9:36</t>
         </is>
       </c>
-      <c r="E141" t="inlineStr">
-        <is>
-          <t>-0.17%</t>
-        </is>
-      </c>
+      <c r="E141" t="inlineStr"/>
       <c r="F141" t="inlineStr">
         <is>
-          <t>资产重组</t>
+          <t>-0.17% 资产重组</t>
         </is>
       </c>
     </row>
@@ -5587,14 +5399,10 @@
           <t>10:24</t>
         </is>
       </c>
-      <c r="E142" t="inlineStr">
-        <is>
-          <t>-0.44%</t>
-        </is>
-      </c>
+      <c r="E142" t="inlineStr"/>
       <c r="F142" t="inlineStr">
         <is>
-          <t>大消费</t>
+          <t>-0.44% 大消费</t>
         </is>
       </c>
     </row>
@@ -5618,7 +5426,7 @@
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>板块标题全部识别成功，各板块声明数量与提取股票数一致，自动校验通过。</t>
+          <t>03/04均识别成功，板块标题与声明数量校验通过。</t>
         </is>
       </c>
     </row>

--- a/excelDataSource/20260623_涨停复盘_verified.xlsx
+++ b/excelDataSource/20260623_涨停复盘_verified.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" windowWidth="24220" windowHeight="9880" tabRatio="600" firstSheet="0" activeTab="1" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="03提取" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="04提取" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet3" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="03提取" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="04提取" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Sheet3" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="191029" fullCalcOnLoad="1"/>
@@ -1048,7 +1048,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F145"/>
+  <dimension ref="A1:F97"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="14"/>
   <cols>
     <col width="6.36363636363636" customWidth="1" style="1" min="2" max="2"/>
@@ -4062,1369 +4062,25 @@
         </is>
       </c>
     </row>
-    <row r="95">
-      <c r="A95" t="inlineStr">
-        <is>
-          <t>涨停停板</t>
-        </is>
-      </c>
-      <c r="B95" t="inlineStr">
-        <is>
-          <t>688179</t>
-        </is>
-      </c>
-      <c r="C95" t="inlineStr">
-        <is>
-          <t>阿拉丁</t>
-        </is>
-      </c>
-      <c r="D95" t="inlineStr">
-        <is>
-          <t>10:55</t>
-        </is>
-      </c>
-      <c r="E95" t="inlineStr"/>
-      <c r="F95" t="inlineStr">
-        <is>
-          <t>18.13% 半导体</t>
-        </is>
-      </c>
-    </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>涨停停板</t>
+          <t>【校验结果】</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>300077</t>
-        </is>
-      </c>
-      <c r="C96" t="inlineStr">
-        <is>
-          <t>国民技术</t>
-        </is>
-      </c>
-      <c r="D96" t="inlineStr">
-        <is>
-          <t>10:23</t>
-        </is>
-      </c>
-      <c r="E96" t="inlineStr"/>
-      <c r="F96" t="inlineStr">
-        <is>
-          <t>15.71% 半导体</t>
+          <t>通过 (verified)</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>涨停停板</t>
+          <t>说明</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
-        <is>
-          <t>300046</t>
-        </is>
-      </c>
-      <c r="C97" t="inlineStr">
-        <is>
-          <t>台基股份</t>
-        </is>
-      </c>
-      <c r="D97" t="inlineStr">
-        <is>
-          <t>10:50</t>
-        </is>
-      </c>
-      <c r="E97" t="inlineStr"/>
-      <c r="F97" t="inlineStr">
-        <is>
-          <t>12.42% 国产芯片</t>
-        </is>
-      </c>
-    </row>
-    <row r="98">
-      <c r="A98" t="inlineStr">
-        <is>
-          <t>涨停停板</t>
-        </is>
-      </c>
-      <c r="B98" t="inlineStr">
-        <is>
-          <t>301399</t>
-        </is>
-      </c>
-      <c r="C98" t="inlineStr">
-        <is>
-          <t>英特科技</t>
-        </is>
-      </c>
-      <c r="D98" t="inlineStr">
-        <is>
-          <t>9:33</t>
-        </is>
-      </c>
-      <c r="E98" t="inlineStr"/>
-      <c r="F98" t="inlineStr">
-        <is>
-          <t>11.24% 液冷服务器</t>
-        </is>
-      </c>
-    </row>
-    <row r="99">
-      <c r="A99" t="inlineStr">
-        <is>
-          <t>涨停停板</t>
-        </is>
-      </c>
-      <c r="B99" t="inlineStr">
-        <is>
-          <t>688105</t>
-        </is>
-      </c>
-      <c r="C99" t="inlineStr">
-        <is>
-          <t>诺唯赞</t>
-        </is>
-      </c>
-      <c r="D99" t="inlineStr">
-        <is>
-          <t>10:39</t>
-        </is>
-      </c>
-      <c r="E99" t="inlineStr"/>
-      <c r="F99" t="inlineStr">
-        <is>
-          <t>11.13% 医药</t>
-        </is>
-      </c>
-    </row>
-    <row r="100">
-      <c r="A100" t="inlineStr">
-        <is>
-          <t>涨停停板</t>
-        </is>
-      </c>
-      <c r="B100" t="inlineStr">
-        <is>
-          <t>600322</t>
-        </is>
-      </c>
-      <c r="C100" t="inlineStr">
-        <is>
-          <t>津投城开</t>
-        </is>
-      </c>
-      <c r="D100" t="inlineStr">
-        <is>
-          <t>9:48</t>
-        </is>
-      </c>
-      <c r="E100" t="inlineStr"/>
-      <c r="F100" t="inlineStr">
-        <is>
-          <t>10.15% 地产</t>
-        </is>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101" t="inlineStr">
-        <is>
-          <t>涨停停板</t>
-        </is>
-      </c>
-      <c r="B101" t="inlineStr">
-        <is>
-          <t>002008</t>
-        </is>
-      </c>
-      <c r="C101" t="inlineStr">
-        <is>
-          <t>大族激光</t>
-        </is>
-      </c>
-      <c r="D101" t="inlineStr">
-        <is>
-          <t>10:31</t>
-        </is>
-      </c>
-      <c r="E101" t="inlineStr"/>
-      <c r="F101" t="inlineStr">
-        <is>
-          <t>9.99% PCB板</t>
-        </is>
-      </c>
-    </row>
-    <row r="102">
-      <c r="A102" t="inlineStr">
-        <is>
-          <t>涨停停板</t>
-        </is>
-      </c>
-      <c r="B102" t="inlineStr">
-        <is>
-          <t>600909</t>
-        </is>
-      </c>
-      <c r="C102" t="inlineStr">
-        <is>
-          <t>华安证券</t>
-        </is>
-      </c>
-      <c r="D102" t="inlineStr">
-        <is>
-          <t>10:00</t>
-        </is>
-      </c>
-      <c r="E102" t="inlineStr"/>
-      <c r="F102" t="inlineStr">
-        <is>
-          <t>9.87% 大金融</t>
-        </is>
-      </c>
-    </row>
-    <row r="103">
-      <c r="A103" t="inlineStr">
-        <is>
-          <t>涨停停板</t>
-        </is>
-      </c>
-      <c r="B103" t="inlineStr">
-        <is>
-          <t>001267</t>
-        </is>
-      </c>
-      <c r="C103" t="inlineStr">
-        <is>
-          <t>汇绿生态</t>
-        </is>
-      </c>
-      <c r="D103" t="inlineStr">
-        <is>
-          <t>10:18</t>
-        </is>
-      </c>
-      <c r="E103" t="inlineStr"/>
-      <c r="F103" t="inlineStr">
-        <is>
-          <t>8.81% 光通信</t>
-        </is>
-      </c>
-    </row>
-    <row r="104">
-      <c r="A104" t="inlineStr">
-        <is>
-          <t>涨停停板</t>
-        </is>
-      </c>
-      <c r="B104" t="inlineStr">
-        <is>
-          <t>002392</t>
-        </is>
-      </c>
-      <c r="C104" t="inlineStr">
-        <is>
-          <t>北京利尔</t>
-        </is>
-      </c>
-      <c r="D104" t="inlineStr">
-        <is>
-          <t>13:24</t>
-        </is>
-      </c>
-      <c r="E104" t="inlineStr"/>
-      <c r="F104" t="inlineStr">
-        <is>
-          <t>8.51% 国产芯片</t>
-        </is>
-      </c>
-    </row>
-    <row r="105">
-      <c r="A105" t="inlineStr">
-        <is>
-          <t>涨停停板</t>
-        </is>
-      </c>
-      <c r="B105" t="inlineStr">
-        <is>
-          <t>603916</t>
-        </is>
-      </c>
-      <c r="C105" t="inlineStr">
-        <is>
-          <t>苏博特</t>
-        </is>
-      </c>
-      <c r="D105" t="inlineStr">
-        <is>
-          <t>9:34</t>
-        </is>
-      </c>
-      <c r="E105" t="inlineStr"/>
-      <c r="F105" t="inlineStr">
-        <is>
-          <t>8.25% 数据中心散热</t>
-        </is>
-      </c>
-    </row>
-    <row r="106">
-      <c r="A106" t="inlineStr">
-        <is>
-          <t>涨停停板</t>
-        </is>
-      </c>
-      <c r="B106" t="inlineStr">
-        <is>
-          <t>002653</t>
-        </is>
-      </c>
-      <c r="C106" t="inlineStr">
-        <is>
-          <t>海思科</t>
-        </is>
-      </c>
-      <c r="D106" t="inlineStr">
-        <is>
-          <t>10:18</t>
-        </is>
-      </c>
-      <c r="E106" t="inlineStr"/>
-      <c r="F106" t="inlineStr">
-        <is>
-          <t>8.08% 医药</t>
-        </is>
-      </c>
-    </row>
-    <row r="107">
-      <c r="A107" t="inlineStr">
-        <is>
-          <t>涨停停板</t>
-        </is>
-      </c>
-      <c r="B107" t="inlineStr">
-        <is>
-          <t>603727</t>
-        </is>
-      </c>
-      <c r="C107" t="inlineStr">
-        <is>
-          <t>博迈科</t>
-        </is>
-      </c>
-      <c r="D107" t="inlineStr">
-        <is>
-          <t>13:43</t>
-        </is>
-      </c>
-      <c r="E107" t="inlineStr"/>
-      <c r="F107" t="inlineStr">
-        <is>
-          <t>7.92% 其他</t>
-        </is>
-      </c>
-    </row>
-    <row r="108">
-      <c r="A108" t="inlineStr">
-        <is>
-          <t>涨停停板</t>
-        </is>
-      </c>
-      <c r="B108" t="inlineStr">
-        <is>
-          <t>000721</t>
-        </is>
-      </c>
-      <c r="C108" t="inlineStr">
-        <is>
-          <t>西安饮食</t>
-        </is>
-      </c>
-      <c r="D108" t="inlineStr">
-        <is>
-          <t>14:49</t>
-        </is>
-      </c>
-      <c r="E108" t="inlineStr"/>
-      <c r="F108" t="inlineStr">
-        <is>
-          <t>7.73% 大消费</t>
-        </is>
-      </c>
-    </row>
-    <row r="109">
-      <c r="A109" t="inlineStr">
-        <is>
-          <t>涨停停板</t>
-        </is>
-      </c>
-      <c r="B109" t="inlineStr">
-        <is>
-          <t>002788</t>
-        </is>
-      </c>
-      <c r="C109" t="inlineStr">
-        <is>
-          <t>鹭燕医药</t>
-        </is>
-      </c>
-      <c r="D109" t="inlineStr">
-        <is>
-          <t>9:49</t>
-        </is>
-      </c>
-      <c r="E109" t="inlineStr"/>
-      <c r="F109" t="inlineStr">
-        <is>
-          <t>7.53% 医疗医药</t>
-        </is>
-      </c>
-    </row>
-    <row r="110">
-      <c r="A110" t="inlineStr">
-        <is>
-          <t>涨停停板</t>
-        </is>
-      </c>
-      <c r="B110" t="inlineStr">
-        <is>
-          <t>603351</t>
-        </is>
-      </c>
-      <c r="C110" t="inlineStr">
-        <is>
-          <t>威尔药业</t>
-        </is>
-      </c>
-      <c r="D110" t="inlineStr">
-        <is>
-          <t>10:59</t>
-        </is>
-      </c>
-      <c r="E110" t="inlineStr"/>
-      <c r="F110" t="inlineStr">
-        <is>
-          <t>7.47% 医药</t>
-        </is>
-      </c>
-    </row>
-    <row r="111">
-      <c r="A111" t="inlineStr">
-        <is>
-          <t>涨停停板</t>
-        </is>
-      </c>
-      <c r="B111" t="inlineStr">
-        <is>
-          <t>603261</t>
-        </is>
-      </c>
-      <c r="C111" t="inlineStr">
-        <is>
-          <t>立航科技</t>
-        </is>
-      </c>
-      <c r="D111" t="inlineStr">
-        <is>
-          <t>13:31</t>
-        </is>
-      </c>
-      <c r="E111" t="inlineStr"/>
-      <c r="F111" t="inlineStr">
-        <is>
-          <t>7.26% 其他</t>
-        </is>
-      </c>
-    </row>
-    <row r="112">
-      <c r="A112" t="inlineStr">
-        <is>
-          <t>涨停停板</t>
-        </is>
-      </c>
-      <c r="B112" t="inlineStr">
-        <is>
-          <t>002397</t>
-        </is>
-      </c>
-      <c r="C112" t="inlineStr">
-        <is>
-          <t>梦洁股份</t>
-        </is>
-      </c>
-      <c r="D112" t="inlineStr">
-        <is>
-          <t>10:38</t>
-        </is>
-      </c>
-      <c r="E112" t="inlineStr"/>
-      <c r="F112" t="inlineStr">
-        <is>
-          <t>7.21% 大消费</t>
-        </is>
-      </c>
-    </row>
-    <row r="113">
-      <c r="A113" t="inlineStr">
-        <is>
-          <t>涨停停板</t>
-        </is>
-      </c>
-      <c r="B113" t="inlineStr">
-        <is>
-          <t>605111</t>
-        </is>
-      </c>
-      <c r="C113" t="inlineStr">
-        <is>
-          <t>新洁能</t>
-        </is>
-      </c>
-      <c r="D113" t="inlineStr">
-        <is>
-          <t>10:20</t>
-        </is>
-      </c>
-      <c r="E113" t="inlineStr"/>
-      <c r="F113" t="inlineStr">
-        <is>
-          <t>7.16% 国产芯片</t>
-        </is>
-      </c>
-    </row>
-    <row r="114">
-      <c r="A114" t="inlineStr">
-        <is>
-          <t>涨停停板</t>
-        </is>
-      </c>
-      <c r="B114" t="inlineStr">
-        <is>
-          <t>603716</t>
-        </is>
-      </c>
-      <c r="C114" t="inlineStr">
-        <is>
-          <t>塞力医疗</t>
-        </is>
-      </c>
-      <c r="D114" t="inlineStr">
-        <is>
-          <t>9:50</t>
-        </is>
-      </c>
-      <c r="E114" t="inlineStr"/>
-      <c r="F114" t="inlineStr">
-        <is>
-          <t>6.62% 医疗医药</t>
-        </is>
-      </c>
-    </row>
-    <row r="115">
-      <c r="A115" t="inlineStr">
-        <is>
-          <t>涨停停板</t>
-        </is>
-      </c>
-      <c r="B115" t="inlineStr">
-        <is>
-          <t>000530</t>
-        </is>
-      </c>
-      <c r="C115" t="inlineStr">
-        <is>
-          <t>冰山冷热</t>
-        </is>
-      </c>
-      <c r="D115" t="inlineStr">
-        <is>
-          <t>9:33</t>
-        </is>
-      </c>
-      <c r="E115" t="inlineStr"/>
-      <c r="F115" t="inlineStr">
-        <is>
-          <t>6.53% 液冷服务器</t>
-        </is>
-      </c>
-    </row>
-    <row r="116">
-      <c r="A116" t="inlineStr">
-        <is>
-          <t>涨停停板</t>
-        </is>
-      </c>
-      <c r="B116" t="inlineStr">
-        <is>
-          <t>601162</t>
-        </is>
-      </c>
-      <c r="C116" t="inlineStr">
-        <is>
-          <t>天风证券</t>
-        </is>
-      </c>
-      <c r="D116" t="inlineStr">
-        <is>
-          <t>9:49</t>
-        </is>
-      </c>
-      <c r="E116" t="inlineStr"/>
-      <c r="F116" t="inlineStr">
-        <is>
-          <t>6.51% 大金融</t>
-        </is>
-      </c>
-    </row>
-    <row r="117">
-      <c r="A117" t="inlineStr">
-        <is>
-          <t>涨停停板</t>
-        </is>
-      </c>
-      <c r="B117" t="inlineStr">
-        <is>
-          <t>000751</t>
-        </is>
-      </c>
-      <c r="C117" t="inlineStr">
-        <is>
-          <t>锌业股份</t>
-        </is>
-      </c>
-      <c r="D117" t="inlineStr">
-        <is>
-          <t>9:25</t>
-        </is>
-      </c>
-      <c r="E117" t="inlineStr"/>
-      <c r="F117" t="inlineStr">
-        <is>
-          <t>6.35% 有色金属</t>
-        </is>
-      </c>
-    </row>
-    <row r="118">
-      <c r="A118" t="inlineStr">
-        <is>
-          <t>涨停停板</t>
-        </is>
-      </c>
-      <c r="B118" t="inlineStr">
-        <is>
-          <t>605288</t>
-        </is>
-      </c>
-      <c r="C118" t="inlineStr">
-        <is>
-          <t>凯迪股份</t>
-        </is>
-      </c>
-      <c r="D118" t="inlineStr">
-        <is>
-          <t>13:37</t>
-        </is>
-      </c>
-      <c r="E118" t="inlineStr"/>
-      <c r="F118" t="inlineStr">
-        <is>
-          <t>6.24% 机器人</t>
-        </is>
-      </c>
-    </row>
-    <row r="119">
-      <c r="A119" t="inlineStr">
-        <is>
-          <t>涨停停板</t>
-        </is>
-      </c>
-      <c r="B119" t="inlineStr">
-        <is>
-          <t>600977</t>
-        </is>
-      </c>
-      <c r="C119" t="inlineStr">
-        <is>
-          <t>中国电影</t>
-        </is>
-      </c>
-      <c r="D119" t="inlineStr">
-        <is>
-          <t>11:07</t>
-        </is>
-      </c>
-      <c r="E119" t="inlineStr"/>
-      <c r="F119" t="inlineStr">
-        <is>
-          <t>6.19% 影视</t>
-        </is>
-      </c>
-    </row>
-    <row r="120">
-      <c r="A120" t="inlineStr">
-        <is>
-          <t>涨停停板</t>
-        </is>
-      </c>
-      <c r="B120" t="inlineStr">
-        <is>
-          <t>603350</t>
-        </is>
-      </c>
-      <c r="C120" t="inlineStr">
-        <is>
-          <t>安乃达</t>
-        </is>
-      </c>
-      <c r="D120" t="inlineStr">
-        <is>
-          <t>10:21</t>
-        </is>
-      </c>
-      <c r="E120" t="inlineStr"/>
-      <c r="F120" t="inlineStr">
-        <is>
-          <t>6.14% 机器人</t>
-        </is>
-      </c>
-    </row>
-    <row r="121">
-      <c r="A121" t="inlineStr">
-        <is>
-          <t>涨停停板</t>
-        </is>
-      </c>
-      <c r="B121" t="inlineStr">
-        <is>
-          <t>002940</t>
-        </is>
-      </c>
-      <c r="C121" t="inlineStr">
-        <is>
-          <t>昂利康</t>
-        </is>
-      </c>
-      <c r="D121" t="inlineStr">
-        <is>
-          <t>9:51</t>
-        </is>
-      </c>
-      <c r="E121" t="inlineStr"/>
-      <c r="F121" t="inlineStr">
-        <is>
-          <t>5.73% 医药</t>
-        </is>
-      </c>
-    </row>
-    <row r="122">
-      <c r="A122" t="inlineStr">
-        <is>
-          <t>涨停停板</t>
-        </is>
-      </c>
-      <c r="B122" t="inlineStr">
-        <is>
-          <t>000703</t>
-        </is>
-      </c>
-      <c r="C122" t="inlineStr">
-        <is>
-          <t>恒逸石化</t>
-        </is>
-      </c>
-      <c r="D122" t="inlineStr">
-        <is>
-          <t>9:58</t>
-        </is>
-      </c>
-      <c r="E122" t="inlineStr"/>
-      <c r="F122" t="inlineStr">
-        <is>
-          <t>5.60% 石油化工</t>
-        </is>
-      </c>
-    </row>
-    <row r="123">
-      <c r="A123" t="inlineStr">
-        <is>
-          <t>涨停停板</t>
-        </is>
-      </c>
-      <c r="B123" t="inlineStr">
-        <is>
-          <t>002837</t>
-        </is>
-      </c>
-      <c r="C123" t="inlineStr">
-        <is>
-          <t>英维克</t>
-        </is>
-      </c>
-      <c r="D123" t="inlineStr">
-        <is>
-          <t>9:25</t>
-        </is>
-      </c>
-      <c r="E123" t="inlineStr"/>
-      <c r="F123" t="inlineStr">
-        <is>
-          <t>5.41% 数据中心散热</t>
-        </is>
-      </c>
-    </row>
-    <row r="124">
-      <c r="A124" t="inlineStr">
-        <is>
-          <t>涨停停板</t>
-        </is>
-      </c>
-      <c r="B124" t="inlineStr">
-        <is>
-          <t>300420</t>
-        </is>
-      </c>
-      <c r="C124" t="inlineStr">
-        <is>
-          <t>五洋自控</t>
-        </is>
-      </c>
-      <c r="D124" t="inlineStr">
-        <is>
-          <t>9:25</t>
-        </is>
-      </c>
-      <c r="E124" t="inlineStr"/>
-      <c r="F124" t="inlineStr">
-        <is>
-          <t>5.40% 数据中心散热</t>
-        </is>
-      </c>
-    </row>
-    <row r="125">
-      <c r="A125" t="inlineStr">
-        <is>
-          <t>涨停停板</t>
-        </is>
-      </c>
-      <c r="B125" t="inlineStr">
-        <is>
-          <t>000962</t>
-        </is>
-      </c>
-      <c r="C125" t="inlineStr">
-        <is>
-          <t>东方钽业</t>
-        </is>
-      </c>
-      <c r="D125" t="inlineStr">
-        <is>
-          <t>9:30</t>
-        </is>
-      </c>
-      <c r="E125" t="inlineStr"/>
-      <c r="F125" t="inlineStr">
-        <is>
-          <t>5.20% 有色金属</t>
-        </is>
-      </c>
-    </row>
-    <row r="126">
-      <c r="A126" t="inlineStr">
-        <is>
-          <t>涨停停板</t>
-        </is>
-      </c>
-      <c r="B126" t="inlineStr">
-        <is>
-          <t>002297</t>
-        </is>
-      </c>
-      <c r="C126" t="inlineStr">
-        <is>
-          <t>博云新材</t>
-        </is>
-      </c>
-      <c r="D126" t="inlineStr">
-        <is>
-          <t>9:31</t>
-        </is>
-      </c>
-      <c r="E126" t="inlineStr"/>
-      <c r="F126" t="inlineStr">
-        <is>
-          <t>5.19% 培育钻石</t>
-        </is>
-      </c>
-    </row>
-    <row r="127">
-      <c r="A127" t="inlineStr">
-        <is>
-          <t>涨停停板</t>
-        </is>
-      </c>
-      <c r="B127" t="inlineStr">
-        <is>
-          <t>603663</t>
-        </is>
-      </c>
-      <c r="C127" t="inlineStr">
-        <is>
-          <t>三祥新材</t>
-        </is>
-      </c>
-      <c r="D127" t="inlineStr">
-        <is>
-          <t>10:00</t>
-        </is>
-      </c>
-      <c r="E127" t="inlineStr"/>
-      <c r="F127" t="inlineStr">
-        <is>
-          <t>5.02% 有色金属</t>
-        </is>
-      </c>
-    </row>
-    <row r="128">
-      <c r="A128" t="inlineStr">
-        <is>
-          <t>涨停停板</t>
-        </is>
-      </c>
-      <c r="B128" t="inlineStr">
-        <is>
-          <t>002418</t>
-        </is>
-      </c>
-      <c r="C128" t="inlineStr">
-        <is>
-          <t>康盛股份</t>
-        </is>
-      </c>
-      <c r="D128" t="inlineStr">
-        <is>
-          <t>9:25</t>
-        </is>
-      </c>
-      <c r="E128" t="inlineStr"/>
-      <c r="F128" t="inlineStr">
-        <is>
-          <t>4.51% 数据中心散热</t>
-        </is>
-      </c>
-    </row>
-    <row r="129">
-      <c r="A129" t="inlineStr">
-        <is>
-          <t>涨停停板</t>
-        </is>
-      </c>
-      <c r="B129" t="inlineStr">
-        <is>
-          <t>002657</t>
-        </is>
-      </c>
-      <c r="C129" t="inlineStr">
-        <is>
-          <t>中科金财</t>
-        </is>
-      </c>
-      <c r="D129" t="inlineStr">
-        <is>
-          <t>9:37</t>
-        </is>
-      </c>
-      <c r="E129" t="inlineStr"/>
-      <c r="F129" t="inlineStr">
-        <is>
-          <t>4.50% 大金融</t>
-        </is>
-      </c>
-    </row>
-    <row r="130">
-      <c r="A130" t="inlineStr">
-        <is>
-          <t>涨停停板</t>
-        </is>
-      </c>
-      <c r="B130" t="inlineStr">
-        <is>
-          <t>600961</t>
-        </is>
-      </c>
-      <c r="C130" t="inlineStr">
-        <is>
-          <t>株冶集团</t>
-        </is>
-      </c>
-      <c r="D130" t="inlineStr">
-        <is>
-          <t>9:25</t>
-        </is>
-      </c>
-      <c r="E130" t="inlineStr"/>
-      <c r="F130" t="inlineStr">
-        <is>
-          <t>4.42% 有色金属</t>
-        </is>
-      </c>
-    </row>
-    <row r="131">
-      <c r="A131" t="inlineStr">
-        <is>
-          <t>涨停停板</t>
-        </is>
-      </c>
-      <c r="B131" t="inlineStr">
-        <is>
-          <t>002640</t>
-        </is>
-      </c>
-      <c r="C131" t="inlineStr">
-        <is>
-          <t>跨境通</t>
-        </is>
-      </c>
-      <c r="D131" t="inlineStr">
-        <is>
-          <t>9:57</t>
-        </is>
-      </c>
-      <c r="E131" t="inlineStr"/>
-      <c r="F131" t="inlineStr">
-        <is>
-          <t>4.19% 其他</t>
-        </is>
-      </c>
-    </row>
-    <row r="132">
-      <c r="A132" t="inlineStr">
-        <is>
-          <t>涨停停板</t>
-        </is>
-      </c>
-      <c r="B132" t="inlineStr">
-        <is>
-          <t>603065</t>
-        </is>
-      </c>
-      <c r="C132" t="inlineStr">
-        <is>
-          <t>宿迁联盛</t>
-        </is>
-      </c>
-      <c r="D132" t="inlineStr">
-        <is>
-          <t>9:37</t>
-        </is>
-      </c>
-      <c r="E132" t="inlineStr"/>
-      <c r="F132" t="inlineStr">
-        <is>
-          <t>4.19% 光通信</t>
-        </is>
-      </c>
-    </row>
-    <row r="133">
-      <c r="A133" t="inlineStr">
-        <is>
-          <t>涨停停板</t>
-        </is>
-      </c>
-      <c r="B133" t="inlineStr">
-        <is>
-          <t>605055</t>
-        </is>
-      </c>
-      <c r="C133" t="inlineStr">
-        <is>
-          <t>迎丰股份</t>
-        </is>
-      </c>
-      <c r="D133" t="inlineStr">
-        <is>
-          <t>10:32</t>
-        </is>
-      </c>
-      <c r="E133" t="inlineStr"/>
-      <c r="F133" t="inlineStr">
-        <is>
-          <t>3.87% 机器人</t>
-        </is>
-      </c>
-    </row>
-    <row r="134">
-      <c r="A134" t="inlineStr">
-        <is>
-          <t>涨停停板</t>
-        </is>
-      </c>
-      <c r="B134" t="inlineStr">
-        <is>
-          <t>603588</t>
-        </is>
-      </c>
-      <c r="C134" t="inlineStr">
-        <is>
-          <t>高能环境</t>
-        </is>
-      </c>
-      <c r="D134" t="inlineStr">
-        <is>
-          <t>9:32</t>
-        </is>
-      </c>
-      <c r="E134" t="inlineStr"/>
-      <c r="F134" t="inlineStr">
-        <is>
-          <t>3.58% 有色金属</t>
-        </is>
-      </c>
-    </row>
-    <row r="135">
-      <c r="A135" t="inlineStr">
-        <is>
-          <t>涨停停板</t>
-        </is>
-      </c>
-      <c r="B135" t="inlineStr">
-        <is>
-          <t>603767</t>
-        </is>
-      </c>
-      <c r="C135" t="inlineStr">
-        <is>
-          <t>中马传动</t>
-        </is>
-      </c>
-      <c r="D135" t="inlineStr">
-        <is>
-          <t>10:05</t>
-        </is>
-      </c>
-      <c r="E135" t="inlineStr"/>
-      <c r="F135" t="inlineStr">
-        <is>
-          <t>3.52% 机器人</t>
-        </is>
-      </c>
-    </row>
-    <row r="136">
-      <c r="A136" t="inlineStr">
-        <is>
-          <t>涨停停板</t>
-        </is>
-      </c>
-      <c r="B136" t="inlineStr">
-        <is>
-          <t>003018</t>
-        </is>
-      </c>
-      <c r="C136" t="inlineStr">
-        <is>
-          <t>金富科技</t>
-        </is>
-      </c>
-      <c r="D136" t="inlineStr">
-        <is>
-          <t>9:25</t>
-        </is>
-      </c>
-      <c r="E136" t="inlineStr"/>
-      <c r="F136" t="inlineStr">
-        <is>
-          <t>2.56% 数据中心散热</t>
-        </is>
-      </c>
-    </row>
-    <row r="137">
-      <c r="A137" t="inlineStr">
-        <is>
-          <t>涨停停板</t>
-        </is>
-      </c>
-      <c r="B137" t="inlineStr">
-        <is>
-          <t>603386</t>
-        </is>
-      </c>
-      <c r="C137" t="inlineStr">
-        <is>
-          <t>骏亚科技</t>
-        </is>
-      </c>
-      <c r="D137" t="inlineStr">
-        <is>
-          <t>9:25</t>
-        </is>
-      </c>
-      <c r="E137" t="inlineStr"/>
-      <c r="F137" t="inlineStr">
-        <is>
-          <t>2.11% 公告</t>
-        </is>
-      </c>
-    </row>
-    <row r="138">
-      <c r="A138" t="inlineStr">
-        <is>
-          <t>涨停停板</t>
-        </is>
-      </c>
-      <c r="B138" t="inlineStr">
-        <is>
-          <t>002947</t>
-        </is>
-      </c>
-      <c r="C138" t="inlineStr">
-        <is>
-          <t>恒铭达</t>
-        </is>
-      </c>
-      <c r="D138" t="inlineStr">
-        <is>
-          <t>9:30</t>
-        </is>
-      </c>
-      <c r="E138" t="inlineStr"/>
-      <c r="F138" t="inlineStr">
-        <is>
-          <t>1.07% 液冷服务器</t>
-        </is>
-      </c>
-    </row>
-    <row r="139">
-      <c r="A139" t="inlineStr">
-        <is>
-          <t>涨停停板</t>
-        </is>
-      </c>
-      <c r="B139" t="inlineStr">
-        <is>
-          <t>002470</t>
-        </is>
-      </c>
-      <c r="C139" t="inlineStr">
-        <is>
-          <t>金正大</t>
-        </is>
-      </c>
-      <c r="D139" t="inlineStr">
-        <is>
-          <t>9:32</t>
-        </is>
-      </c>
-      <c r="E139" t="inlineStr"/>
-      <c r="F139" t="inlineStr">
-        <is>
-          <t>0.92% 石油化工</t>
-        </is>
-      </c>
-    </row>
-    <row r="140">
-      <c r="A140" t="inlineStr">
-        <is>
-          <t>涨停停板</t>
-        </is>
-      </c>
-      <c r="B140" t="inlineStr">
-        <is>
-          <t>002963</t>
-        </is>
-      </c>
-      <c r="C140" t="inlineStr">
-        <is>
-          <t>豪尔赛</t>
-        </is>
-      </c>
-      <c r="D140" t="inlineStr">
-        <is>
-          <t>9:30</t>
-        </is>
-      </c>
-      <c r="E140" t="inlineStr"/>
-      <c r="F140" t="inlineStr">
-        <is>
-          <t>0.28% 其他</t>
-        </is>
-      </c>
-    </row>
-    <row r="141">
-      <c r="A141" t="inlineStr">
-        <is>
-          <t>涨停停板</t>
-        </is>
-      </c>
-      <c r="B141" t="inlineStr">
-        <is>
-          <t>002655</t>
-        </is>
-      </c>
-      <c r="C141" t="inlineStr">
-        <is>
-          <t>共达电声</t>
-        </is>
-      </c>
-      <c r="D141" t="inlineStr">
-        <is>
-          <t>9:36</t>
-        </is>
-      </c>
-      <c r="E141" t="inlineStr"/>
-      <c r="F141" t="inlineStr">
-        <is>
-          <t>-0.17% 资产重组</t>
-        </is>
-      </c>
-    </row>
-    <row r="142">
-      <c r="A142" t="inlineStr">
-        <is>
-          <t>涨停停板</t>
-        </is>
-      </c>
-      <c r="B142" t="inlineStr">
-        <is>
-          <t>002853</t>
-        </is>
-      </c>
-      <c r="C142" t="inlineStr">
-        <is>
-          <t>皮阿诺</t>
-        </is>
-      </c>
-      <c r="D142" t="inlineStr">
-        <is>
-          <t>10:24</t>
-        </is>
-      </c>
-      <c r="E142" t="inlineStr"/>
-      <c r="F142" t="inlineStr">
-        <is>
-          <t>-0.44% 大消费</t>
-        </is>
-      </c>
-    </row>
-    <row r="144">
-      <c r="A144" t="inlineStr">
-        <is>
-          <t>【校验结果】</t>
-        </is>
-      </c>
-      <c r="B144" t="inlineStr">
-        <is>
-          <t>通过 (verified)</t>
-        </is>
-      </c>
-    </row>
-    <row r="145">
-      <c r="A145" t="inlineStr">
-        <is>
-          <t>说明</t>
-        </is>
-      </c>
-      <c r="B145" t="inlineStr">
         <is>
           <t>03/04均识别成功，板块标题与声明数量校验通过。</t>
         </is>
